--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_simple.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.3465346534653465</v>
+        <v>0.33</v>
       </c>
       <c r="B2">
-        <v>0.04</v>
+        <v>0.04347826086956522</v>
       </c>
       <c r="C2">
-        <v>0.3571428571428572</v>
+        <v>0.3642857142857143</v>
       </c>
       <c r="D2">
-        <v>0.7142857142857143</v>
+        <v>0.7235772357723578</v>
       </c>
       <c r="E2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G2">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
